--- a/backend/static_assets/SPOT_Customer_QtyBand_Chart.xlsx
+++ b/backend/static_assets/SPOT_Customer_QtyBand_Chart.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Customer × Qty Band" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Median" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Avg (Mean)" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -203,7 +204,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Customer × Qty Band'!B4</f>
+              <f>'Median'!B4</f>
             </strRef>
           </tx>
           <spPr>
@@ -213,12 +214,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Customer × Qty Band'!$A$5:$A$19</f>
+              <f>'Median'!$A$5:$A$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Customer × Qty Band'!$B$5:$B$19</f>
+              <f>'Median'!$B$5:$B$19</f>
             </numRef>
           </val>
         </ser>
@@ -227,7 +228,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Customer × Qty Band'!C4</f>
+              <f>'Median'!C4</f>
             </strRef>
           </tx>
           <spPr>
@@ -237,12 +238,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Customer × Qty Band'!$A$5:$A$19</f>
+              <f>'Median'!$A$5:$A$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Customer × Qty Band'!$C$5:$C$19</f>
+              <f>'Median'!$C$5:$C$19</f>
             </numRef>
           </val>
         </ser>
@@ -251,7 +252,7 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'Customer × Qty Band'!D4</f>
+              <f>'Median'!D4</f>
             </strRef>
           </tx>
           <spPr>
@@ -261,12 +262,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Customer × Qty Band'!$A$5:$A$19</f>
+              <f>'Median'!$A$5:$A$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Customer × Qty Band'!$D$5:$D$19</f>
+              <f>'Median'!$D$5:$D$19</f>
             </numRef>
           </val>
         </ser>
@@ -275,7 +276,7 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'Customer × Qty Band'!E4</f>
+              <f>'Median'!E4</f>
             </strRef>
           </tx>
           <spPr>
@@ -285,12 +286,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Customer × Qty Band'!$A$5:$A$19</f>
+              <f>'Median'!$A$5:$A$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Customer × Qty Band'!$E$5:$E$19</f>
+              <f>'Median'!$E$5:$E$19</f>
             </numRef>
           </val>
         </ser>
@@ -299,7 +300,7 @@
           <order val="4"/>
           <tx>
             <strRef>
-              <f>'Customer × Qty Band'!F4</f>
+              <f>'Median'!F4</f>
             </strRef>
           </tx>
           <spPr>
@@ -309,12 +310,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Customer × Qty Band'!$A$5:$A$19</f>
+              <f>'Median'!$A$5:$A$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Customer × Qty Band'!$F$5:$F$19</f>
+              <f>'Median'!$F$5:$F$19</f>
             </numRef>
           </val>
         </ser>
@@ -384,7 +385,243 @@
 </chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="11"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Avg Variance % — by Customer × Qty Band</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Avg (Mean)'!B4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Avg (Mean)'!$A$5:$A$19</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Avg (Mean)'!$B$5:$B$19</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Avg (Mean)'!C4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Avg (Mean)'!$A$5:$A$19</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Avg (Mean)'!$C$5:$C$19</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Avg (Mean)'!D4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Avg (Mean)'!$A$5:$A$19</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Avg (Mean)'!$D$5:$D$19</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Avg (Mean)'!E4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Avg (Mean)'!$A$5:$A$19</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Avg (Mean)'!$E$5:$E$19</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="4"/>
+          <order val="4"/>
+          <tx>
+            <strRef>
+              <f>'Avg (Mean)'!F4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Avg (Mean)'!$A$5:$A$19</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Avg (Mean)'!$F$5:$F$19</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Avg Variance %</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Customer</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="11520000" cy="7920000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -722,7 +959,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Quote-total level. Cells show median variance (SPOT vs iQuote). Green = SPOT cheaper, Red = SPOT more expensive, White = near parity. Blank cell = no quotes from that customer in that qty band.</t>
+          <t>Quote-total level. Green = SPOT cheaper, Red = SPOT more expensive, White = near parity. Blank cell = no quotes from that customer in that qty band.</t>
         </is>
       </c>
     </row>
@@ -1094,4 +1331,406 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Variance % — Top 15 Customers × Qty Band</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Quote-total level. Green = SPOT cheaper, Red = SPOT more expensive, White = near parity. Blank cell = no quotes from that customer in that qty band.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Customer</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>1-49</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>50-199</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>200-999</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>1000-4999</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>5000+</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Quote Count</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Apex Display Group</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>35.90653605565359</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-13.45422907107912</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>15.17307220042718</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>8.827360078840293</v>
+      </c>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="6" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Skybox Packaging, LLC</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>38.94091639821357</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>2.960367327211211</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>16.21273643451724</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>-9.268851812370757</v>
+      </c>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="6" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>McElroy Contract Packaging, Inc.</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="5" t="n">
+        <v>39.26495297605675</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>35.34249013428767</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>27.91070584328644</v>
+      </c>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="6" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>PCA Pennsylvania Acquisition Corporation</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="5" t="n">
+        <v>3.753494963422579</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>23.96737655953212</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>13.79005223995886</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>65.57995076887907</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>PCA - Akron</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>56.92758476349936</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>29.30130994668932</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>18.06115108087893</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>8.108483683442572</v>
+      </c>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="6" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Massillon Container</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>-10.77085781433607</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>27.45532640314835</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>27.35576923076924</v>
+      </c>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="6" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>PCA - Ashland</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>26.79580696584707</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>27.8076979100926</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>54.53371229848384</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>10.62485447917098</v>
+      </c>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="6" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>BCI Knoxville Division</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="5" t="n">
+        <v>2.317255854164451</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>23.84440573497768</v>
+      </c>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="6" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Tavens</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="5" t="n">
+        <v>5.368803355554134</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-1.884904877076758</v>
+      </c>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="6" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Packaging Corporation</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="n">
+        <v>-22.76854871668291</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-26.68606553161489</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>PCA- New Oxford</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>122.4210371664149</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>148.4066559725991</v>
+      </c>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="6" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>PCA / Fairfield, OH</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="5" t="n">
+        <v>39.37401442309388</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>34.19798276077477</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-5.530480119787563</v>
+      </c>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="6" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Weber Display &amp; Packaging</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>41.45047005974158</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>17.41923973136595</v>
+      </c>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n">
+        <v>-2.602053762715559</v>
+      </c>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="6" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>International Paper Retail Pkg &amp; Display</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>36.13415672797537</v>
+      </c>
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="6" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>BCI Tennessee Division</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="5" t="n">
+        <v>4.2185790251675</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>11.75767403602361</v>
+      </c>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="6" t="n">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="B5:F19">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="num" val="-30"/>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="150"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
 </file>